--- a/configs/import.xlsx
+++ b/configs/import.xlsx
@@ -5,11 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Dev1" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Dev2" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,21 +22,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
-  <si>
-    <t xml:space="preserve">HostConnectType:</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="23">
+  <si>
+    <t xml:space="preserve">Host:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ConType:</t>
   </si>
   <si>
     <t xml:space="preserve">Address:</t>
   </si>
   <si>
+    <t xml:space="preserve">Port:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Modbus-TCP</t>
   </si>
   <si>
-    <t xml:space="preserve">127.0.0.1:502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devices:</t>
+    <t xml:space="preserve">127.0.0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Device:</t>
   </si>
   <si>
     <t xml:space="preserve">Comment:</t>
@@ -44,31 +54,43 @@
     <t xml:space="preserve">NetAddr:</t>
   </si>
   <si>
-    <t xml:space="preserve">ConnectType:</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dev1</t>
   </si>
   <si>
     <t xml:space="preserve">Эмулятор слейва</t>
   </si>
   <si>
-    <t xml:space="preserve">Type:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Access:</t>
+    <t xml:space="preserve">Dev2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataType:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TimeScan:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dev1_Var_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Int</t>
   </si>
   <si>
     <t xml:space="preserve">Тестовая переменная 1</t>
   </si>
   <si>
-    <t xml:space="preserve">HoldingRegister</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R</t>
+    <t xml:space="preserve">Dev1_Var_1</t>
   </si>
   <si>
     <t xml:space="preserve">Тестовая переменная 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dev1_Var_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тестовая переменная 3</t>
   </si>
 </sst>
 </file>
@@ -144,8 +166,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -154,6 +180,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -346,68 +376,97 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.25"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.84"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13" min="5" style="1" width="8.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="18.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="18.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="17.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="13.84"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="14" min="6" style="2" width="8.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>502</v>
+      </c>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>2</v>
-      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -425,55 +484,176 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.68"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13" min="4" style="1" width="10.16"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="15.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="15.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="27.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="19.11"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="6" style="2" width="10.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>11</v>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;KffffffСтраница &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="27.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="19.11"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>14</v>
+      <c r="B2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/configs/import.xlsx
+++ b/configs/import.xlsx
@@ -790,7 +790,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="10.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="20.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="15.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="38.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="43.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="14.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="22.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="17.39"/>
@@ -1128,7 +1128,7 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
@@ -1151,7 +1151,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="n">
         <v>0</v>
       </c>
@@ -1331,7 +1331,7 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="n">
         <v>0</v>
       </c>
